--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6589" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6589" uniqueCount="586">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -549,7 +549,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>2032: reference from AR TRANSACTION - BILL NUMBER &gt; ACCOUNTS RECEIVABLE - DEBTOR (433-.03 &gt; 430-9)</t>
+    <t>2032: reference based on AR TRANSACTION - BILL NUMBER &gt; ACCOUNTS RECEIVABLE - DEBTOR (433-.03 &gt; 430-9)</t>
   </si>
   <si>
     <t>IB.ARTransaction.AccountsReceivableIEN,IB.ARTransaction.PatientIEN,IB.ARTransactionComment.PatientIEN,IB.ARTransactionDescription.PatientIEN,IB.ARTransactionFiscalYear.PatientIEN
@@ -795,7 +795,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1979: source value from AR TRANSACTION - BILL NUMBER (433-.03)</t>
+    <t>1979: source value based on AR TRANSACTION - BILL NUMBER (433-.03)</t>
   </si>
   <si>
     <t>IB.ARTransaction.AccountsReceivableIEN,IB.ARTransaction.PatientIEN,IB.ARTransactionComment.PatientIEN,IB.ARTransactionDescription.PatientIEN,IB.ARTransactionFiscalYear.PatientIEN</t>
@@ -953,7 +953,7 @@
     <t>PaymentReconciliation.identifier.value</t>
   </si>
   <si>
-    <t>1978: source value from AR TRANSACTION - TRANSACTION NUMBER (433-.01)</t>
+    <t>1978: source value based on AR TRANSACTION - TRANSACTION NUMBER (433-.01)</t>
   </si>
   <si>
     <t>IB.ARTransaction.TransactionNumber</t>
@@ -1026,7 +1026,7 @@
     <t>Need to record a timestamp for use by both the recipient and the issuer.</t>
   </si>
   <si>
-    <t>1984: source value from AR TRANSACTION - DATE ENTERED (433-19)</t>
+    <t>1984: source value based on AR TRANSACTION - DATE ENTERED (433-19)</t>
   </si>
   <si>
     <t>IB.ARTransaction.EnteredDateTime</t>
@@ -1133,7 +1133,11 @@
     <t>Provided for user display.</t>
   </si>
   <si>
-    <t>1982: source value from AR TRANSACTION - TRANSACTION TYPE &gt; ACCOUNTS RECEIVABLE TRANS.TYPE - NAME (433-12 &gt; 430.3-.01) case IEN = 34 OR 2</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+dppr-31-1982:If IEN = 34 OR 2 then source value from (433-12 &gt; 430.3-.01) {null}</t>
+  </si>
+  <si>
+    <t>1982: source value based on AR TRANSACTION - TRANSACTION TYPE &gt; ACCOUNTS RECEIVABLE TRANS.TYPE - NAME (433-12 &gt; 430.3-.01) if IEN = 34 OR 2</t>
   </si>
   <si>
     <t>IB.ARTransaction.ARTransactionTypeIEN
@@ -1159,7 +1163,7 @@
     <t>To advise the payee when payment can be expected.</t>
   </si>
   <si>
-    <t>1981: source value from AR TRANSACTION - TRANSACTION DATE (433-11)</t>
+    <t>1981: source value based on AR TRANSACTION - TRANSACTION DATE (433-11)</t>
   </si>
   <si>
     <t>IB.ARTransaction.TransactionDateTime,IB.ARTransactionComment.TransactionDateTime,IB.ARTransactionDescription.TransactionDateTime,IB.ARTransactionFiscalYear.TransactionDateTime</t>
@@ -1181,7 +1185,7 @@
     <t>Needed to provide the actual payment amount.</t>
   </si>
   <si>
-    <t>1983: source value from AR TRANSACTION - TRANS. AMOUNT (433-15)</t>
+    <t>1983: source value based on AR TRANSACTION - TRANS. AMOUNT (433-15)</t>
   </si>
   <si>
     <t>IB.ARTransaction.TransactionAmount</t>
@@ -1202,7 +1206,7 @@
     <t>Enable the receiver to reconcile when payment is received.</t>
   </si>
   <si>
-    <t>1985: source value from AR TRANSACTION - RECEIPT # (433-13)</t>
+    <t>1985: source value based on AR TRANSACTION - RECEIPT # (433-13)</t>
   </si>
   <si>
     <t>IB.ARTransaction.ReceiptNumber</t>
@@ -1457,7 +1461,7 @@
     <t>PaymentReconciliation.detail:va-principal-collected.amount</t>
   </si>
   <si>
-    <t>1986: source value from AR TRANSACTION - PRIN.COLLECTED (433-31)</t>
+    <t>1986: source value based on AR TRANSACTION - PRIN.COLLECTED (433-31)</t>
   </si>
   <si>
     <t>IB.ARTransaction.PrincipaAmountCollected</t>
@@ -1526,7 +1530,7 @@
     <t>PaymentReconciliation.detail:va-interest-collected.amount</t>
   </si>
   <si>
-    <t>1987: source value from AR TRANSACTION - INTEREST COLLECTED (433-32)</t>
+    <t>1987: source value based on AR TRANSACTION - INTEREST COLLECTED (433-32)</t>
   </si>
   <si>
     <t>IB.ARTransaction.InterestAmountCollected</t>
@@ -1595,7 +1599,7 @@
     <t>PaymentReconciliation.detail:va-admin-collected.amount</t>
   </si>
   <si>
-    <t>1988: source value from AR TRANSACTION - ADMIN.COLLECTED (433-33)</t>
+    <t>1988: source value based on AR TRANSACTION - ADMIN.COLLECTED (433-33)</t>
   </si>
   <si>
     <t>IB.ARTransaction.AdministrativeAmountCollected</t>
@@ -1664,7 +1668,7 @@
     <t>PaymentReconciliation.detail:va-marshal-collected.amount</t>
   </si>
   <si>
-    <t>1989: source value from AR TRANSACTION - MARSHAL FEE COLLECTED (433-34)</t>
+    <t>1989: source value based on AR TRANSACTION - MARSHAL FEE COLLECTED (433-34)</t>
   </si>
   <si>
     <t>IB.ARTransaction.MarshalFeeAmountCollected</t>
@@ -1733,7 +1737,7 @@
     <t>PaymentReconciliation.detail:va-courtcost-collected.amount</t>
   </si>
   <si>
-    <t>1990: source value from AR TRANSACTION - COURT COST COLLECTED (433-35)</t>
+    <t>1990: source value based on AR TRANSACTION - COURT COST COLLECTED (433-35)</t>
   </si>
   <si>
     <t>IB.ARTransaction.CourtCostCollected</t>
@@ -2166,7 +2170,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="143.01953125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="144.0546875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="175.2265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -9111,16 +9115,16 @@
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>361</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>79</v>
@@ -9134,10 +9138,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9160,17 +9164,17 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -9219,7 +9223,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>89</v>
@@ -9234,10 +9238,10 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
@@ -9254,10 +9258,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9280,17 +9284,17 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9339,7 +9343,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>89</v>
@@ -9354,10 +9358,10 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -9374,10 +9378,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9403,16 +9407,16 @@
         <v>181</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9461,7 +9465,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9476,10 +9480,10 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
@@ -9496,10 +9500,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9522,17 +9526,17 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -9569,7 +9573,7 @@
         <v>79</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
@@ -9579,7 +9583,7 @@
         <v>138</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9614,10 +9618,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9732,10 +9736,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9852,14 +9856,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9881,10 +9885,10 @@
         <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>189</v>
@@ -9939,7 +9943,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9974,10 +9978,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10003,14 +10007,14 @@
         <v>181</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -10059,7 +10063,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10094,10 +10098,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10123,14 +10127,14 @@
         <v>181</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -10179,7 +10183,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10214,10 +10218,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10243,16 +10247,16 @@
         <v>203</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10277,13 +10281,13 @@
         <v>79</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>79</v>
@@ -10301,7 +10305,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>89</v>
@@ -10336,10 +10340,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10362,17 +10366,17 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -10421,7 +10425,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10456,10 +10460,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10485,14 +10489,14 @@
         <v>345</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
@@ -10541,7 +10545,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10576,10 +10580,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10602,17 +10606,17 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10661,7 +10665,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10696,10 +10700,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10722,17 +10726,17 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -10781,7 +10785,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10816,10 +10820,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10842,17 +10846,17 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10901,7 +10905,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10936,10 +10940,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10965,14 +10969,14 @@
         <v>345</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -11021,7 +11025,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11056,10 +11060,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11082,17 +11086,17 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11141,7 +11145,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11176,13 +11180,13 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>79</v>
@@ -11204,17 +11208,17 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>79</v>
@@ -11263,7 +11267,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11298,10 +11302,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11416,10 +11420,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11536,14 +11540,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11565,10 +11569,10 @@
         <v>134</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>189</v>
@@ -11623,7 +11627,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11658,10 +11662,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11687,14 +11691,14 @@
         <v>181</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -11743,7 +11747,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11778,10 +11782,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11807,14 +11811,14 @@
         <v>181</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -11863,7 +11867,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11898,10 +11902,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11927,16 +11931,16 @@
         <v>203</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
@@ -11961,13 +11965,13 @@
         <v>79</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>79</v>
@@ -11985,7 +11989,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>89</v>
@@ -12020,10 +12024,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12138,10 +12142,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12258,10 +12262,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12380,10 +12384,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12428,7 +12432,7 @@
         <v>79</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>79</v>
@@ -12482,7 +12486,7 @@
         <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>79</v>
@@ -12502,10 +12506,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12528,17 +12532,17 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>79</v>
@@ -12587,7 +12591,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12622,10 +12626,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12651,14 +12655,14 @@
         <v>345</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>79</v>
@@ -12707,7 +12711,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12742,10 +12746,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12768,17 +12772,17 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12827,7 +12831,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12862,10 +12866,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12888,17 +12892,17 @@
         <v>79</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>79</v>
@@ -12947,7 +12951,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12982,10 +12986,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13008,17 +13012,17 @@
         <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13067,7 +13071,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13102,10 +13106,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13131,14 +13135,14 @@
         <v>345</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13187,7 +13191,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13222,10 +13226,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13248,17 +13252,17 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -13307,7 +13311,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13322,10 +13326,10 @@
         <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>79</v>
@@ -13342,13 +13346,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>79</v>
@@ -13370,17 +13374,17 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>79</v>
@@ -13429,7 +13433,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13464,10 +13468,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13582,10 +13586,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13702,14 +13706,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13731,10 +13735,10 @@
         <v>134</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>189</v>
@@ -13789,7 +13793,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13824,10 +13828,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13853,14 +13857,14 @@
         <v>181</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>79</v>
@@ -13909,7 +13913,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13944,10 +13948,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13973,14 +13977,14 @@
         <v>181</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>79</v>
@@ -14029,7 +14033,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14064,10 +14068,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14093,16 +14097,16 @@
         <v>203</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -14127,13 +14131,13 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>79</v>
@@ -14151,7 +14155,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>89</v>
@@ -14186,10 +14190,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14304,10 +14308,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14424,10 +14428,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14546,10 +14550,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14594,7 +14598,7 @@
         <v>79</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>79</v>
@@ -14648,7 +14652,7 @@
         <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>79</v>
@@ -14668,10 +14672,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14694,17 +14698,17 @@
         <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>79</v>
@@ -14753,7 +14757,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14788,10 +14792,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14817,14 +14821,14 @@
         <v>345</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>79</v>
@@ -14873,7 +14877,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14908,10 +14912,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14934,17 +14938,17 @@
         <v>79</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -14993,7 +14997,7 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15028,10 +15032,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15054,17 +15058,17 @@
         <v>79</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>79</v>
@@ -15113,7 +15117,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15148,10 +15152,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15174,17 +15178,17 @@
         <v>79</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>79</v>
@@ -15233,7 +15237,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15268,10 +15272,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15297,14 +15301,14 @@
         <v>345</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>79</v>
@@ -15353,7 +15357,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15388,10 +15392,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15414,17 +15418,17 @@
         <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>79</v>
@@ -15473,7 +15477,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15488,10 +15492,10 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>79</v>
@@ -15508,13 +15512,13 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>79</v>
@@ -15536,17 +15540,17 @@
         <v>79</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>79</v>
@@ -15595,7 +15599,7 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15630,10 +15634,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15748,10 +15752,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15868,14 +15872,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -15897,10 +15901,10 @@
         <v>134</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>189</v>
@@ -15955,7 +15959,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -15990,10 +15994,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16019,14 +16023,14 @@
         <v>181</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -16075,7 +16079,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16110,10 +16114,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16139,14 +16143,14 @@
         <v>181</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>79</v>
@@ -16195,7 +16199,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16230,10 +16234,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16259,16 +16263,16 @@
         <v>203</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>79</v>
@@ -16293,13 +16297,13 @@
         <v>79</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>79</v>
@@ -16317,7 +16321,7 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>89</v>
@@ -16352,10 +16356,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16470,10 +16474,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16590,10 +16594,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16712,10 +16716,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16760,7 +16764,7 @@
         <v>79</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>79</v>
@@ -16814,7 +16818,7 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>79</v>
@@ -16834,10 +16838,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16860,17 +16864,17 @@
         <v>79</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>79</v>
@@ -16919,7 +16923,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16954,10 +16958,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16983,14 +16987,14 @@
         <v>345</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
@@ -17039,7 +17043,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17074,10 +17078,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17100,17 +17104,17 @@
         <v>79</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>79</v>
@@ -17159,7 +17163,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17194,10 +17198,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17220,17 +17224,17 @@
         <v>79</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>79</v>
@@ -17279,7 +17283,7 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17314,10 +17318,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17340,17 +17344,17 @@
         <v>79</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>79</v>
@@ -17399,7 +17403,7 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17434,10 +17438,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17463,14 +17467,14 @@
         <v>345</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -17519,7 +17523,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17554,10 +17558,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17580,17 +17584,17 @@
         <v>79</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>79</v>
@@ -17639,7 +17643,7 @@
         <v>79</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17654,10 +17658,10 @@
         <v>101</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>79</v>
@@ -17674,13 +17678,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>79</v>
@@ -17702,17 +17706,17 @@
         <v>79</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>79</v>
@@ -17761,7 +17765,7 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17796,10 +17800,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17914,10 +17918,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18034,14 +18038,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18063,10 +18067,10 @@
         <v>134</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>189</v>
@@ -18121,7 +18125,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18156,10 +18160,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18185,14 +18189,14 @@
         <v>181</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>79</v>
@@ -18241,7 +18245,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18276,10 +18280,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18305,14 +18309,14 @@
         <v>181</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>79</v>
@@ -18361,7 +18365,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18396,10 +18400,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18425,16 +18429,16 @@
         <v>203</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>79</v>
@@ -18459,13 +18463,13 @@
         <v>79</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>79</v>
@@ -18483,7 +18487,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>89</v>
@@ -18518,10 +18522,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18636,10 +18640,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18756,10 +18760,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18878,10 +18882,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18926,7 +18930,7 @@
         <v>79</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>79</v>
@@ -18980,7 +18984,7 @@
         <v>101</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>79</v>
@@ -19000,10 +19004,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19026,17 +19030,17 @@
         <v>79</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>79</v>
@@ -19085,7 +19089,7 @@
         <v>79</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19120,10 +19124,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19149,14 +19153,14 @@
         <v>345</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>79</v>
@@ -19205,7 +19209,7 @@
         <v>79</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19240,10 +19244,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19266,17 +19270,17 @@
         <v>79</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>79</v>
@@ -19325,7 +19329,7 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19360,10 +19364,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19386,17 +19390,17 @@
         <v>79</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>79</v>
@@ -19445,7 +19449,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19480,10 +19484,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19506,17 +19510,17 @@
         <v>79</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -19565,7 +19569,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -19600,10 +19604,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19629,14 +19633,14 @@
         <v>345</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -19685,7 +19689,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -19720,10 +19724,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19746,17 +19750,17 @@
         <v>79</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -19805,7 +19809,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -19820,10 +19824,10 @@
         <v>101</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>79</v>
@@ -19840,13 +19844,13 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D148" t="s" s="2">
         <v>79</v>
@@ -19868,17 +19872,17 @@
         <v>79</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>79</v>
@@ -19927,7 +19931,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -19962,10 +19966,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20080,10 +20084,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20200,14 +20204,14 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -20229,10 +20233,10 @@
         <v>134</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N151" t="s" s="2">
         <v>189</v>
@@ -20287,7 +20291,7 @@
         <v>79</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20322,10 +20326,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20351,14 +20355,14 @@
         <v>181</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>79</v>
@@ -20407,7 +20411,7 @@
         <v>79</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20442,10 +20446,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20471,14 +20475,14 @@
         <v>181</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>79</v>
@@ -20527,7 +20531,7 @@
         <v>79</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20562,10 +20566,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20591,16 +20595,16 @@
         <v>203</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>79</v>
@@ -20625,13 +20629,13 @@
         <v>79</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>79</v>
@@ -20649,7 +20653,7 @@
         <v>79</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>89</v>
@@ -20684,10 +20688,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20802,10 +20806,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20922,10 +20926,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21044,10 +21048,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21092,7 +21096,7 @@
         <v>79</v>
       </c>
       <c r="S158" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="T158" t="s" s="2">
         <v>79</v>
@@ -21146,7 +21150,7 @@
         <v>101</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>79</v>
@@ -21166,10 +21170,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21192,17 +21196,17 @@
         <v>79</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>79</v>
@@ -21251,7 +21255,7 @@
         <v>79</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21286,10 +21290,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21315,14 +21319,14 @@
         <v>345</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>79</v>
@@ -21371,7 +21375,7 @@
         <v>79</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21406,10 +21410,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21432,17 +21436,17 @@
         <v>79</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>79</v>
@@ -21491,7 +21495,7 @@
         <v>79</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -21526,10 +21530,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21552,17 +21556,17 @@
         <v>79</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>79</v>
@@ -21611,7 +21615,7 @@
         <v>79</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -21646,10 +21650,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21672,17 +21676,17 @@
         <v>79</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>79</v>
@@ -21731,7 +21735,7 @@
         <v>79</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -21766,10 +21770,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21795,14 +21799,14 @@
         <v>345</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>79</v>
@@ -21851,7 +21855,7 @@
         <v>79</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -21886,10 +21890,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21912,17 +21916,17 @@
         <v>79</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>79</v>
@@ -21971,7 +21975,7 @@
         <v>79</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -21986,10 +21990,10 @@
         <v>101</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>79</v>
@@ -22006,10 +22010,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22035,16 +22039,16 @@
         <v>203</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>79</v>
@@ -22069,13 +22073,13 @@
         <v>79</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>79</v>
@@ -22093,7 +22097,7 @@
         <v>79</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22128,10 +22132,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22154,17 +22158,17 @@
         <v>79</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>79</v>
@@ -22213,7 +22217,7 @@
         <v>79</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22248,10 +22252,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22366,10 +22370,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22486,14 +22490,14 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
@@ -22515,10 +22519,10 @@
         <v>134</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N170" t="s" s="2">
         <v>189</v>
@@ -22573,7 +22577,7 @@
         <v>79</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22608,10 +22612,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22637,14 +22641,14 @@
         <v>109</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>79</v>
@@ -22672,10 +22676,10 @@
         <v>196</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>79</v>
@@ -22693,7 +22697,7 @@
         <v>79</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -22728,10 +22732,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22757,14 +22761,14 @@
         <v>149</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>79</v>
@@ -22813,7 +22817,7 @@
         <v>79</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -22840,7 +22844,7 @@
         <v>79</v>
       </c>
       <c r="AO172" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AP172" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1134,7 +1134,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dppr-31-1982:If IEN = 34 OR 2 then source value from (433-12 &gt; 430.3-.01) {null}</t>
+dppr-31-1982:If IEN = 34 OR 2 then source value from (433-12 &gt; 430.3-.01) {true}</t>
   </si>
   <si>
     <t>1982: source value based on AR TRANSACTION - TRANSACTION TYPE &gt; ACCOUNTS RECEIVABLE TRANS.TYPE - NAME (433-12 &gt; 430.3-.01) if IEN = 34 OR 2</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$176</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6589" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6741" uniqueCount="603">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1185,10 +1185,62 @@
     <t>Needed to provide the actual payment amount.</t>
   </si>
   <si>
+    <t>PaymentReconciliation.paymentAmount.id</t>
+  </si>
+  <si>
+    <t>PaymentReconciliation.paymentAmount.extension</t>
+  </si>
+  <si>
+    <t>PaymentReconciliation.paymentAmount.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision).</t>
+  </si>
+  <si>
+    <t>Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>The amount of the currency. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>Money.value</t>
+  </si>
+  <si>
     <t>1983: source value based on AR TRANSACTION - TRANS. AMOUNT (433-15)</t>
   </si>
   <si>
     <t>IB.ARTransaction.TransactionAmount</t>
+  </si>
+  <si>
+    <t>PaymentReconciliation.paymentAmount.currency</t>
+  </si>
+  <si>
+    <t>ISO 4217 Currency Code</t>
+  </si>
+  <si>
+    <t>ISO 4217 Currency Code.</t>
+  </si>
+  <si>
+    <t>A code indicating the currency, taken from ISO 4217.</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/currencies|4.0.1</t>
+  </si>
+  <si>
+    <t>Money.currency</t>
+  </si>
+  <si>
+    <t>1983-1: fixed value = #USD</t>
   </si>
   <si>
     <t>PaymentReconciliation.paymentIdentifier</t>
@@ -2132,7 +2184,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP172"/>
+  <dimension ref="A1:AP176"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="103.5859375" customWidth="true" bestFit="true"/>
@@ -9275,7 +9327,7 @@
         <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>79</v>
@@ -9358,10 +9410,10 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>377</v>
+        <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -9378,10 +9430,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9395,7 +9447,7 @@
         <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>79</v>
@@ -9404,20 +9456,16 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>380</v>
+        <v>150</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
       </c>
@@ -9465,7 +9513,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>379</v>
+        <v>152</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9477,13 +9525,13 @@
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>384</v>
+        <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>385</v>
+        <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
@@ -9495,19 +9543,19 @@
         <v>79</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9526,18 +9574,18 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>387</v>
+        <v>134</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>388</v>
+        <v>187</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>79</v>
       </c>
@@ -9573,9 +9621,11 @@
         <v>79</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AC62" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="AD62" t="s" s="2">
         <v>79</v>
       </c>
@@ -9583,7 +9633,7 @@
         <v>138</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>386</v>
+        <v>157</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9595,7 +9645,7 @@
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
@@ -9613,15 +9663,15 @@
         <v>79</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9635,25 +9685,29 @@
         <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>149</v>
+        <v>380</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>150</v>
+        <v>381</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9701,7 +9755,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>152</v>
+        <v>385</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9713,13 +9767,13 @@
         <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>79</v>
+        <v>386</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>79</v>
+        <v>387</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -9731,49 +9785,49 @@
         <v>79</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>187</v>
+        <v>389</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
       </c>
@@ -9782,7 +9836,7 @@
         <v>79</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>79</v>
@@ -9797,13 +9851,13 @@
         <v>79</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -9821,22 +9875,22 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>157</v>
+        <v>394</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>79</v>
@@ -9851,50 +9905,50 @@
         <v>79</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>189</v>
+        <v>399</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>282</v>
+        <v>400</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9943,25 +9997,25 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>79</v>
+        <v>401</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
@@ -9973,15 +10027,15 @@
         <v>79</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9992,7 +10046,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>79</v>
@@ -10004,17 +10058,17 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>181</v>
+        <v>404</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -10051,25 +10105,23 @@
         <v>79</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>79</v>
@@ -10098,10 +10150,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10124,18 +10176,16 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>404</v>
+        <v>150</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>405</v>
+        <v>151</v>
       </c>
       <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>402</v>
-      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>79</v>
       </c>
@@ -10183,7 +10233,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>403</v>
+        <v>152</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10195,7 +10245,7 @@
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>79</v>
@@ -10213,26 +10263,26 @@
         <v>79</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>79</v>
@@ -10244,20 +10294,18 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>203</v>
+        <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>407</v>
+        <v>187</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>408</v>
+        <v>188</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>79</v>
       </c>
@@ -10281,13 +10329,13 @@
         <v>79</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>79</v>
@@ -10305,19 +10353,19 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>406</v>
+        <v>157</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>79</v>
@@ -10335,48 +10383,50 @@
         <v>79</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>415</v>
+        <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O69" t="s" s="2">
-        <v>418</v>
+        <v>282</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -10425,19 +10475,19 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
@@ -10455,15 +10505,15 @@
         <v>79</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10486,17 +10536,17 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>345</v>
+        <v>181</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
@@ -10545,7 +10595,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10580,10 +10630,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10606,17 +10656,17 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>415</v>
+        <v>181</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10665,7 +10715,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10700,10 +10750,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10711,7 +10761,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>89</v>
@@ -10726,17 +10776,19 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>366</v>
+        <v>203</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -10761,13 +10813,13 @@
         <v>79</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>79</v>
+        <v>430</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>79</v>
@@ -10785,10 +10837,10 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>89</v>
@@ -10820,10 +10872,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10846,17 +10898,17 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10905,7 +10957,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10940,10 +10992,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10969,14 +11021,14 @@
         <v>345</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -11025,7 +11077,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11060,10 +11112,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11086,17 +11138,17 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11145,7 +11197,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11180,14 +11232,12 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>79</v>
       </c>
@@ -11208,17 +11258,17 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>79</v>
@@ -11267,13 +11317,13 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>79</v>
@@ -11302,10 +11352,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>392</v>
+        <v>447</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11328,16 +11378,18 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>149</v>
+        <v>448</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>150</v>
+        <v>449</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>151</v>
+        <v>450</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>79</v>
       </c>
@@ -11385,7 +11437,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>152</v>
+        <v>447</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11397,7 +11449,7 @@
         <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>79</v>
@@ -11415,26 +11467,26 @@
         <v>79</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>393</v>
+        <v>452</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>79</v>
@@ -11446,18 +11498,18 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>134</v>
+        <v>345</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>187</v>
+        <v>453</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
       </c>
@@ -11505,19 +11557,19 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>157</v>
+        <v>452</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
@@ -11535,50 +11587,48 @@
         <v>79</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>394</v>
+        <v>455</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>134</v>
+        <v>373</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>396</v>
+        <v>456</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>282</v>
+        <v>458</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -11627,19 +11677,19 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>398</v>
+        <v>455</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>79</v>
@@ -11657,17 +11707,19 @@
         <v>79</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C80" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="D80" t="s" s="2">
         <v>79</v>
       </c>
@@ -11688,17 +11740,17 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>181</v>
+        <v>404</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -11747,13 +11799,13 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>79</v>
@@ -11782,10 +11834,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11808,18 +11860,16 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>404</v>
+        <v>150</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>405</v>
+        <v>151</v>
       </c>
       <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>402</v>
-      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>79</v>
       </c>
@@ -11867,7 +11917,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>403</v>
+        <v>152</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11879,7 +11929,7 @@
         <v>79</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>79</v>
@@ -11897,26 +11947,26 @@
         <v>79</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>79</v>
@@ -11928,20 +11978,18 @@
         <v>79</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>203</v>
+        <v>134</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>407</v>
+        <v>187</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>408</v>
+        <v>188</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>79</v>
       </c>
@@ -11965,13 +12013,13 @@
         <v>79</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>79</v>
@@ -11989,19 +12037,19 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>406</v>
+        <v>157</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>79</v>
@@ -12019,47 +12067,51 @@
         <v>79</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>451</v>
+        <v>411</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>150</v>
+        <v>413</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
       </c>
@@ -12107,19 +12159,19 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>79</v>
@@ -12137,26 +12189,26 @@
         <v>79</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>153</v>
+        <v>132</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>79</v>
@@ -12168,18 +12220,18 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>187</v>
+        <v>417</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
       </c>
@@ -12215,31 +12267,31 @@
         <v>79</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>157</v>
+        <v>416</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>79</v>
@@ -12257,15 +12309,15 @@
         <v>79</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>455</v>
+        <v>420</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12276,7 +12328,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>79</v>
@@ -12285,22 +12337,20 @@
         <v>79</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>219</v>
+        <v>421</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>222</v>
+        <v>419</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>79</v>
@@ -12349,13 +12399,13 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>223</v>
+        <v>420</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>79</v>
@@ -12379,15 +12429,15 @@
         <v>79</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>224</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>457</v>
+        <v>423</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12395,34 +12445,34 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>227</v>
+        <v>424</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>228</v>
+        <v>425</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>229</v>
+        <v>426</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>230</v>
+        <v>427</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>79</v>
@@ -12432,7 +12482,7 @@
         <v>79</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>458</v>
+        <v>79</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>79</v>
@@ -12447,13 +12497,13 @@
         <v>79</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>79</v>
+        <v>430</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>79</v>
@@ -12471,10 +12521,10 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>232</v>
+        <v>423</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>89</v>
@@ -12486,7 +12536,7 @@
         <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>459</v>
+        <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>79</v>
@@ -12501,15 +12551,15 @@
         <v>79</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>414</v>
+        <v>468</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12532,18 +12582,16 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>415</v>
+        <v>149</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>416</v>
+        <v>150</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>417</v>
+        <v>151</v>
       </c>
       <c r="N87" s="2"/>
-      <c r="O87" t="s" s="2">
-        <v>418</v>
-      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>79</v>
       </c>
@@ -12591,7 +12639,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>414</v>
+        <v>152</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12603,7 +12651,7 @@
         <v>79</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>79</v>
@@ -12621,26 +12669,26 @@
         <v>79</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>419</v>
+        <v>470</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>79</v>
@@ -12652,18 +12700,18 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>345</v>
+        <v>134</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>420</v>
+        <v>187</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>79</v>
       </c>
@@ -12699,31 +12747,31 @@
         <v>79</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>419</v>
+        <v>157</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>79</v>
@@ -12741,15 +12789,15 @@
         <v>79</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>423</v>
+        <v>472</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12760,7 +12808,7 @@
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>79</v>
@@ -12769,20 +12817,22 @@
         <v>79</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>415</v>
+        <v>218</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>424</v>
+        <v>219</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="O89" t="s" s="2">
-        <v>426</v>
+        <v>222</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12831,13 +12881,13 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>79</v>
@@ -12861,15 +12911,15 @@
         <v>79</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>79</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>427</v>
+        <v>474</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12883,26 +12933,28 @@
         <v>89</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>366</v>
+        <v>149</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>428</v>
+        <v>227</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O90" t="s" s="2">
-        <v>422</v>
+        <v>230</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>79</v>
@@ -12912,7 +12964,7 @@
         <v>79</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>79</v>
+        <v>475</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>79</v>
@@ -12951,7 +13003,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>427</v>
+        <v>232</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12966,7 +13018,7 @@
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>79</v>
+        <v>476</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>79</v>
@@ -12981,15 +13033,15 @@
         <v>79</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13012,17 +13064,17 @@
         <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13071,7 +13123,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13106,10 +13158,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13135,14 +13187,14 @@
         <v>345</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13191,7 +13243,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13226,10 +13278,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13243,7 +13295,7 @@
         <v>89</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>79</v>
@@ -13252,17 +13304,17 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -13311,7 +13363,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13326,10 +13378,10 @@
         <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>467</v>
+        <v>79</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>468</v>
+        <v>79</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>79</v>
@@ -13346,14 +13398,12 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>79</v>
       </c>
@@ -13374,17 +13424,17 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>79</v>
@@ -13433,13 +13483,13 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>79</v>
@@ -13468,10 +13518,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>392</v>
+        <v>447</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13494,16 +13544,18 @@
         <v>79</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>149</v>
+        <v>448</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>150</v>
+        <v>449</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>151</v>
+        <v>450</v>
       </c>
       <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>79</v>
       </c>
@@ -13551,7 +13603,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>152</v>
+        <v>447</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13563,7 +13615,7 @@
         <v>79</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>79</v>
@@ -13581,26 +13633,26 @@
         <v>79</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>393</v>
+        <v>452</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>79</v>
@@ -13612,18 +13664,18 @@
         <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>134</v>
+        <v>345</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>187</v>
+        <v>453</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>79</v>
       </c>
@@ -13671,19 +13723,19 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>157</v>
+        <v>452</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>79</v>
@@ -13701,50 +13753,48 @@
         <v>79</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>394</v>
+        <v>455</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>134</v>
+        <v>373</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>396</v>
+        <v>456</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>282</v>
+        <v>458</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
@@ -13793,25 +13843,25 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>398</v>
+        <v>455</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>79</v>
+        <v>484</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>79</v>
+        <v>485</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>79</v>
@@ -13823,17 +13873,19 @@
         <v>79</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C98" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="D98" t="s" s="2">
         <v>79</v>
       </c>
@@ -13854,17 +13906,17 @@
         <v>79</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>181</v>
+        <v>404</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>79</v>
@@ -13913,13 +13965,13 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>79</v>
@@ -13948,10 +14000,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13974,18 +14026,16 @@
         <v>79</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>404</v>
+        <v>150</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>405</v>
+        <v>151</v>
       </c>
       <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>402</v>
-      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>79</v>
       </c>
@@ -14033,7 +14083,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>403</v>
+        <v>152</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14045,7 +14095,7 @@
         <v>79</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>79</v>
@@ -14063,26 +14113,26 @@
         <v>79</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>79</v>
@@ -14094,20 +14144,18 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>203</v>
+        <v>134</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>407</v>
+        <v>187</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>408</v>
+        <v>188</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>79</v>
       </c>
@@ -14131,13 +14179,13 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>79</v>
@@ -14155,19 +14203,19 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>406</v>
+        <v>157</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>79</v>
@@ -14185,47 +14233,51 @@
         <v>79</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>451</v>
+        <v>411</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>150</v>
+        <v>413</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>79</v>
       </c>
@@ -14273,19 +14325,19 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>79</v>
@@ -14303,26 +14355,26 @@
         <v>79</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>153</v>
+        <v>132</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>79</v>
@@ -14334,18 +14386,18 @@
         <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>187</v>
+        <v>417</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>79</v>
       </c>
@@ -14381,31 +14433,31 @@
         <v>79</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>157</v>
+        <v>416</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>79</v>
@@ -14423,15 +14475,15 @@
         <v>79</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>455</v>
+        <v>420</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14442,7 +14494,7 @@
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>79</v>
@@ -14451,22 +14503,20 @@
         <v>79</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>219</v>
+        <v>421</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>222</v>
+        <v>419</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>79</v>
@@ -14515,13 +14565,13 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>223</v>
+        <v>420</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>79</v>
@@ -14545,15 +14595,15 @@
         <v>79</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>224</v>
+        <v>79</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>457</v>
+        <v>423</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14561,34 +14611,34 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>227</v>
+        <v>424</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>228</v>
+        <v>425</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>229</v>
+        <v>426</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>230</v>
+        <v>427</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>79</v>
@@ -14598,7 +14648,7 @@
         <v>79</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>481</v>
+        <v>79</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>79</v>
@@ -14613,13 +14663,13 @@
         <v>79</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>79</v>
+        <v>430</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>79</v>
@@ -14637,10 +14687,10 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>232</v>
+        <v>423</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>89</v>
@@ -14652,7 +14702,7 @@
         <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>482</v>
+        <v>79</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>79</v>
@@ -14667,15 +14717,15 @@
         <v>79</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>414</v>
+        <v>468</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14698,18 +14748,16 @@
         <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>415</v>
+        <v>149</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>416</v>
+        <v>150</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>417</v>
+        <v>151</v>
       </c>
       <c r="N105" s="2"/>
-      <c r="O105" t="s" s="2">
-        <v>418</v>
-      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>79</v>
       </c>
@@ -14757,7 +14805,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>414</v>
+        <v>152</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14769,7 +14817,7 @@
         <v>79</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>79</v>
@@ -14787,26 +14835,26 @@
         <v>79</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>419</v>
+        <v>470</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>79</v>
@@ -14818,18 +14866,18 @@
         <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>345</v>
+        <v>134</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>420</v>
+        <v>187</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>79</v>
       </c>
@@ -14865,31 +14913,31 @@
         <v>79</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>419</v>
+        <v>157</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>79</v>
@@ -14907,15 +14955,15 @@
         <v>79</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>423</v>
+        <v>472</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14926,7 +14974,7 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>79</v>
@@ -14935,20 +14983,22 @@
         <v>79</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>415</v>
+        <v>218</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>424</v>
+        <v>219</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N107" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="O107" t="s" s="2">
-        <v>426</v>
+        <v>222</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -14997,13 +15047,13 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>79</v>
@@ -15027,15 +15077,15 @@
         <v>79</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>79</v>
+        <v>224</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>427</v>
+        <v>474</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15049,26 +15099,28 @@
         <v>89</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>366</v>
+        <v>149</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>428</v>
+        <v>227</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O108" t="s" s="2">
-        <v>422</v>
+        <v>230</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>79</v>
@@ -15078,7 +15130,7 @@
         <v>79</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>79</v>
+        <v>498</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>79</v>
@@ -15117,7 +15169,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>427</v>
+        <v>232</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15132,7 +15184,7 @@
         <v>101</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>79</v>
+        <v>499</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>79</v>
@@ -15147,15 +15199,15 @@
         <v>79</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15178,17 +15230,17 @@
         <v>79</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>79</v>
@@ -15237,7 +15289,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15272,10 +15324,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15301,14 +15353,14 @@
         <v>345</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>79</v>
@@ -15357,7 +15409,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15392,10 +15444,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15409,7 +15461,7 @@
         <v>89</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>79</v>
@@ -15418,17 +15470,17 @@
         <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>79</v>
@@ -15477,7 +15529,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15492,10 +15544,10 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>490</v>
+        <v>79</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>491</v>
+        <v>79</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>79</v>
@@ -15512,14 +15564,12 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
         <v>79</v>
       </c>
@@ -15540,17 +15590,17 @@
         <v>79</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>79</v>
@@ -15599,13 +15649,13 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>79</v>
@@ -15634,10 +15684,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>392</v>
+        <v>447</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15660,16 +15710,18 @@
         <v>79</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>149</v>
+        <v>448</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>150</v>
+        <v>449</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>151</v>
+        <v>450</v>
       </c>
       <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
+      <c r="O113" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>79</v>
       </c>
@@ -15717,7 +15769,7 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>152</v>
+        <v>447</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15729,7 +15781,7 @@
         <v>79</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>79</v>
@@ -15747,26 +15799,26 @@
         <v>79</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>393</v>
+        <v>452</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>79</v>
@@ -15778,18 +15830,18 @@
         <v>79</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>134</v>
+        <v>345</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>187</v>
+        <v>453</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O114" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>79</v>
       </c>
@@ -15837,19 +15889,19 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>157</v>
+        <v>452</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>79</v>
@@ -15867,50 +15919,48 @@
         <v>79</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>394</v>
+        <v>455</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>134</v>
+        <v>373</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>396</v>
+        <v>456</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>282</v>
+        <v>458</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>79</v>
@@ -15959,25 +16009,25 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>398</v>
+        <v>455</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>79</v>
+        <v>507</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>79</v>
+        <v>508</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>79</v>
@@ -15989,17 +16039,19 @@
         <v>79</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C116" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="D116" t="s" s="2">
         <v>79</v>
       </c>
@@ -16020,17 +16072,17 @@
         <v>79</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>181</v>
+        <v>404</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -16079,13 +16131,13 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>79</v>
@@ -16114,10 +16166,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16140,18 +16192,16 @@
         <v>79</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>404</v>
+        <v>150</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>405</v>
+        <v>151</v>
       </c>
       <c r="N117" s="2"/>
-      <c r="O117" t="s" s="2">
-        <v>402</v>
-      </c>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>79</v>
       </c>
@@ -16199,7 +16249,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>403</v>
+        <v>152</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16211,7 +16261,7 @@
         <v>79</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>79</v>
@@ -16229,26 +16279,26 @@
         <v>79</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>79</v>
@@ -16260,20 +16310,18 @@
         <v>79</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>203</v>
+        <v>134</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>407</v>
+        <v>187</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>408</v>
+        <v>188</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>79</v>
       </c>
@@ -16297,13 +16345,13 @@
         <v>79</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>79</v>
@@ -16321,19 +16369,19 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>406</v>
+        <v>157</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>79</v>
@@ -16351,47 +16399,51 @@
         <v>79</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>451</v>
+        <v>411</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>150</v>
+        <v>413</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
       </c>
@@ -16439,19 +16491,19 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>79</v>
@@ -16469,26 +16521,26 @@
         <v>79</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>153</v>
+        <v>132</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>79</v>
@@ -16500,18 +16552,18 @@
         <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>187</v>
+        <v>417</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O120" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>79</v>
       </c>
@@ -16547,31 +16599,31 @@
         <v>79</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>157</v>
+        <v>416</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>79</v>
@@ -16589,15 +16641,15 @@
         <v>79</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>455</v>
+        <v>420</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16608,7 +16660,7 @@
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>79</v>
@@ -16617,22 +16669,20 @@
         <v>79</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>219</v>
+        <v>421</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>222</v>
+        <v>419</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>79</v>
@@ -16681,13 +16731,13 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>223</v>
+        <v>420</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>79</v>
@@ -16711,15 +16761,15 @@
         <v>79</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>224</v>
+        <v>79</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>457</v>
+        <v>423</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16727,34 +16777,34 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>227</v>
+        <v>424</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>228</v>
+        <v>425</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>229</v>
+        <v>426</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>230</v>
+        <v>427</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
@@ -16764,7 +16814,7 @@
         <v>79</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>504</v>
+        <v>79</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>79</v>
@@ -16779,13 +16829,13 @@
         <v>79</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>79</v>
+        <v>430</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>79</v>
@@ -16803,10 +16853,10 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>232</v>
+        <v>423</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>89</v>
@@ -16818,7 +16868,7 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>505</v>
+        <v>79</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>79</v>
@@ -16833,15 +16883,15 @@
         <v>79</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>414</v>
+        <v>468</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16864,18 +16914,16 @@
         <v>79</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>415</v>
+        <v>149</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>416</v>
+        <v>150</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>417</v>
+        <v>151</v>
       </c>
       <c r="N123" s="2"/>
-      <c r="O123" t="s" s="2">
-        <v>418</v>
-      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>79</v>
       </c>
@@ -16923,7 +16971,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>414</v>
+        <v>152</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16935,7 +16983,7 @@
         <v>79</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>79</v>
@@ -16953,26 +17001,26 @@
         <v>79</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>419</v>
+        <v>470</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>79</v>
@@ -16984,18 +17032,18 @@
         <v>79</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>345</v>
+        <v>134</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>420</v>
+        <v>187</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>79</v>
       </c>
@@ -17031,31 +17079,31 @@
         <v>79</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>419</v>
+        <v>157</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>79</v>
@@ -17073,15 +17121,15 @@
         <v>79</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>423</v>
+        <v>472</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17092,7 +17140,7 @@
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>79</v>
@@ -17101,20 +17149,22 @@
         <v>79</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>415</v>
+        <v>218</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>424</v>
+        <v>219</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N125" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="O125" t="s" s="2">
-        <v>426</v>
+        <v>222</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>79</v>
@@ -17163,13 +17213,13 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>79</v>
@@ -17193,15 +17243,15 @@
         <v>79</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>79</v>
+        <v>224</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>427</v>
+        <v>474</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17215,26 +17265,28 @@
         <v>89</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>366</v>
+        <v>149</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>428</v>
+        <v>227</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N126" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O126" t="s" s="2">
-        <v>422</v>
+        <v>230</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>79</v>
@@ -17244,7 +17296,7 @@
         <v>79</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>79</v>
+        <v>521</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>79</v>
@@ -17283,7 +17335,7 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>427</v>
+        <v>232</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17298,7 +17350,7 @@
         <v>101</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>79</v>
+        <v>522</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>79</v>
@@ -17313,15 +17365,15 @@
         <v>79</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17344,17 +17396,17 @@
         <v>79</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>79</v>
@@ -17403,7 +17455,7 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17438,10 +17490,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17467,14 +17519,14 @@
         <v>345</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -17523,7 +17575,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17558,10 +17610,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17575,7 +17627,7 @@
         <v>89</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>79</v>
@@ -17584,17 +17636,17 @@
         <v>79</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>79</v>
@@ -17643,7 +17695,7 @@
         <v>79</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17658,10 +17710,10 @@
         <v>101</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>513</v>
+        <v>79</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>79</v>
@@ -17678,14 +17730,12 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C130" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
         <v>79</v>
       </c>
@@ -17706,17 +17756,17 @@
         <v>79</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>79</v>
@@ -17765,13 +17815,13 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>79</v>
@@ -17800,10 +17850,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>392</v>
+        <v>447</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17826,16 +17876,18 @@
         <v>79</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>149</v>
+        <v>448</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>150</v>
+        <v>449</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>151</v>
+        <v>450</v>
       </c>
       <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
+      <c r="O131" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>79</v>
       </c>
@@ -17883,7 +17935,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>152</v>
+        <v>447</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -17895,7 +17947,7 @@
         <v>79</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>79</v>
@@ -17913,26 +17965,26 @@
         <v>79</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>393</v>
+        <v>452</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>79</v>
@@ -17944,18 +17996,18 @@
         <v>79</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>134</v>
+        <v>345</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>187</v>
+        <v>453</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>79</v>
       </c>
@@ -18003,19 +18055,19 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>157</v>
+        <v>452</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>79</v>
@@ -18033,50 +18085,48 @@
         <v>79</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>394</v>
+        <v>455</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>134</v>
+        <v>373</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>396</v>
+        <v>456</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>282</v>
+        <v>458</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>79</v>
@@ -18125,25 +18175,25 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>398</v>
+        <v>455</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>79</v>
+        <v>530</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>79</v>
+        <v>531</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>79</v>
@@ -18155,17 +18205,19 @@
         <v>79</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C134" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="D134" t="s" s="2">
         <v>79</v>
       </c>
@@ -18186,17 +18238,17 @@
         <v>79</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>181</v>
+        <v>404</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>79</v>
@@ -18245,13 +18297,13 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>79</v>
@@ -18280,10 +18332,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18306,18 +18358,16 @@
         <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>404</v>
+        <v>150</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>405</v>
+        <v>151</v>
       </c>
       <c r="N135" s="2"/>
-      <c r="O135" t="s" s="2">
-        <v>402</v>
-      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>79</v>
       </c>
@@ -18365,7 +18415,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>403</v>
+        <v>152</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18377,7 +18427,7 @@
         <v>79</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>79</v>
@@ -18395,26 +18445,26 @@
         <v>79</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>79</v>
@@ -18426,20 +18476,18 @@
         <v>79</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>203</v>
+        <v>134</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>407</v>
+        <v>187</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>408</v>
+        <v>188</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>79</v>
       </c>
@@ -18463,13 +18511,13 @@
         <v>79</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>79</v>
@@ -18487,19 +18535,19 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>406</v>
+        <v>157</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>79</v>
@@ -18517,47 +18565,51 @@
         <v>79</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>451</v>
+        <v>411</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I137" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>150</v>
+        <v>413</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>79</v>
       </c>
@@ -18605,19 +18657,19 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>79</v>
@@ -18635,26 +18687,26 @@
         <v>79</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>153</v>
+        <v>132</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>79</v>
@@ -18666,18 +18718,18 @@
         <v>79</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>187</v>
+        <v>417</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O138" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>79</v>
       </c>
@@ -18713,31 +18765,31 @@
         <v>79</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>157</v>
+        <v>416</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>79</v>
@@ -18755,15 +18807,15 @@
         <v>79</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>455</v>
+        <v>420</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18774,7 +18826,7 @@
         <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>79</v>
@@ -18783,22 +18835,20 @@
         <v>79</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>219</v>
+        <v>421</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>222</v>
+        <v>419</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>79</v>
@@ -18847,13 +18897,13 @@
         <v>79</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>223</v>
+        <v>420</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>79</v>
@@ -18877,15 +18927,15 @@
         <v>79</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>224</v>
+        <v>79</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>457</v>
+        <v>423</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18893,34 +18943,34 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>227</v>
+        <v>424</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>228</v>
+        <v>425</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>229</v>
+        <v>426</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>230</v>
+        <v>427</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>79</v>
@@ -18930,7 +18980,7 @@
         <v>79</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>527</v>
+        <v>79</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>79</v>
@@ -18945,13 +18995,13 @@
         <v>79</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>79</v>
+        <v>430</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>79</v>
@@ -18969,10 +19019,10 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>232</v>
+        <v>423</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>89</v>
@@ -18984,7 +19034,7 @@
         <v>101</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>528</v>
+        <v>79</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>79</v>
@@ -18999,15 +19049,15 @@
         <v>79</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>414</v>
+        <v>468</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19030,18 +19080,16 @@
         <v>79</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>415</v>
+        <v>149</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>416</v>
+        <v>150</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>417</v>
+        <v>151</v>
       </c>
       <c r="N141" s="2"/>
-      <c r="O141" t="s" s="2">
-        <v>418</v>
-      </c>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>79</v>
       </c>
@@ -19089,7 +19137,7 @@
         <v>79</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>414</v>
+        <v>152</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19101,7 +19149,7 @@
         <v>79</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>79</v>
@@ -19119,26 +19167,26 @@
         <v>79</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>419</v>
+        <v>470</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>79</v>
@@ -19150,18 +19198,18 @@
         <v>79</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>345</v>
+        <v>134</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>420</v>
+        <v>187</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>79</v>
       </c>
@@ -19197,31 +19245,31 @@
         <v>79</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>419</v>
+        <v>157</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>79</v>
@@ -19239,15 +19287,15 @@
         <v>79</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>423</v>
+        <v>472</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19258,7 +19306,7 @@
         <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>79</v>
@@ -19267,20 +19315,22 @@
         <v>79</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>415</v>
+        <v>218</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>424</v>
+        <v>219</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N143" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="O143" t="s" s="2">
-        <v>426</v>
+        <v>222</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>79</v>
@@ -19329,13 +19379,13 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>79</v>
@@ -19359,15 +19409,15 @@
         <v>79</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>79</v>
+        <v>224</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>427</v>
+        <v>474</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19381,26 +19431,28 @@
         <v>89</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>366</v>
+        <v>149</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>428</v>
+        <v>227</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N144" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O144" t="s" s="2">
-        <v>422</v>
+        <v>230</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>79</v>
@@ -19410,7 +19462,7 @@
         <v>79</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>79</v>
+        <v>544</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>79</v>
@@ -19449,7 +19501,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>427</v>
+        <v>232</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19464,7 +19516,7 @@
         <v>101</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>79</v>
+        <v>545</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>79</v>
@@ -19479,15 +19531,15 @@
         <v>79</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19510,17 +19562,17 @@
         <v>79</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -19569,7 +19621,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -19604,10 +19656,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19633,14 +19685,14 @@
         <v>345</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -19689,7 +19741,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -19724,10 +19776,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19741,7 +19793,7 @@
         <v>89</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>79</v>
@@ -19750,17 +19802,17 @@
         <v>79</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -19809,7 +19861,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -19824,10 +19876,10 @@
         <v>101</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>536</v>
+        <v>79</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>537</v>
+        <v>79</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>79</v>
@@ -19844,14 +19896,12 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C148" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
         <v>79</v>
       </c>
@@ -19872,17 +19922,17 @@
         <v>79</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>79</v>
@@ -19931,13 +19981,13 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>79</v>
@@ -19966,10 +20016,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>392</v>
+        <v>447</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19992,16 +20042,18 @@
         <v>79</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>149</v>
+        <v>448</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>150</v>
+        <v>449</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>151</v>
+        <v>450</v>
       </c>
       <c r="N149" s="2"/>
-      <c r="O149" s="2"/>
+      <c r="O149" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P149" t="s" s="2">
         <v>79</v>
       </c>
@@ -20049,7 +20101,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>152</v>
+        <v>447</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20061,7 +20113,7 @@
         <v>79</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>79</v>
@@ -20079,26 +20131,26 @@
         <v>79</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>393</v>
+        <v>452</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>79</v>
@@ -20110,18 +20162,18 @@
         <v>79</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>134</v>
+        <v>345</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>187</v>
+        <v>453</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O150" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N150" s="2"/>
+      <c r="O150" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P150" t="s" s="2">
         <v>79</v>
       </c>
@@ -20169,19 +20221,19 @@
         <v>79</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>157</v>
+        <v>452</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>79</v>
@@ -20199,50 +20251,48 @@
         <v>79</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>394</v>
+        <v>455</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I151" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>134</v>
+        <v>373</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>396</v>
+        <v>456</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>282</v>
+        <v>458</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>79</v>
@@ -20291,25 +20341,25 @@
         <v>79</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>398</v>
+        <v>455</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>79</v>
+        <v>553</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>79</v>
+        <v>554</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>79</v>
@@ -20321,17 +20371,19 @@
         <v>79</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C152" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="C152" t="s" s="2">
+        <v>556</v>
+      </c>
       <c r="D152" t="s" s="2">
         <v>79</v>
       </c>
@@ -20352,17 +20404,17 @@
         <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>181</v>
+        <v>404</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>79</v>
@@ -20411,13 +20463,13 @@
         <v>79</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>79</v>
@@ -20446,10 +20498,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20472,18 +20524,16 @@
         <v>79</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>404</v>
+        <v>150</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>405</v>
+        <v>151</v>
       </c>
       <c r="N153" s="2"/>
-      <c r="O153" t="s" s="2">
-        <v>402</v>
-      </c>
+      <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>79</v>
       </c>
@@ -20531,7 +20581,7 @@
         <v>79</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>403</v>
+        <v>152</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20543,7 +20593,7 @@
         <v>79</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>79</v>
@@ -20561,26 +20611,26 @@
         <v>79</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>79</v>
@@ -20592,20 +20642,18 @@
         <v>79</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>203</v>
+        <v>134</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>407</v>
+        <v>187</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>408</v>
+        <v>188</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>79</v>
       </c>
@@ -20629,13 +20677,13 @@
         <v>79</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>79</v>
@@ -20653,19 +20701,19 @@
         <v>79</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>406</v>
+        <v>157</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>79</v>
@@ -20683,47 +20731,51 @@
         <v>79</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>451</v>
+        <v>411</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I155" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>150</v>
+        <v>413</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P155" t="s" s="2">
         <v>79</v>
       </c>
@@ -20771,19 +20823,19 @@
         <v>79</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>79</v>
@@ -20801,26 +20853,26 @@
         <v>79</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>153</v>
+        <v>132</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>79</v>
@@ -20832,18 +20884,18 @@
         <v>79</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>187</v>
+        <v>417</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O156" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N156" s="2"/>
+      <c r="O156" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P156" t="s" s="2">
         <v>79</v>
       </c>
@@ -20879,31 +20931,31 @@
         <v>79</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>157</v>
+        <v>416</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>79</v>
@@ -20921,15 +20973,15 @@
         <v>79</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>455</v>
+        <v>420</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20940,7 +20992,7 @@
         <v>80</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>79</v>
@@ -20949,22 +21001,20 @@
         <v>79</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>219</v>
+        <v>421</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>222</v>
+        <v>419</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>79</v>
@@ -21013,13 +21063,13 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>223</v>
+        <v>420</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>79</v>
@@ -21043,15 +21093,15 @@
         <v>79</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>224</v>
+        <v>79</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>457</v>
+        <v>423</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21059,34 +21109,34 @@
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G158" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>227</v>
+        <v>424</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>228</v>
+        <v>425</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>229</v>
+        <v>426</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>230</v>
+        <v>427</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>79</v>
@@ -21096,7 +21146,7 @@
         <v>79</v>
       </c>
       <c r="S158" t="s" s="2">
-        <v>550</v>
+        <v>79</v>
       </c>
       <c r="T158" t="s" s="2">
         <v>79</v>
@@ -21111,13 +21161,13 @@
         <v>79</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>79</v>
+        <v>430</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>79</v>
@@ -21135,10 +21185,10 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>232</v>
+        <v>423</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>89</v>
@@ -21150,7 +21200,7 @@
         <v>101</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>551</v>
+        <v>79</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>79</v>
@@ -21165,15 +21215,15 @@
         <v>79</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>414</v>
+        <v>468</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21196,18 +21246,16 @@
         <v>79</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>415</v>
+        <v>149</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>416</v>
+        <v>150</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>417</v>
+        <v>151</v>
       </c>
       <c r="N159" s="2"/>
-      <c r="O159" t="s" s="2">
-        <v>418</v>
-      </c>
+      <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>79</v>
       </c>
@@ -21255,7 +21303,7 @@
         <v>79</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>414</v>
+        <v>152</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21267,7 +21315,7 @@
         <v>79</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>79</v>
@@ -21285,26 +21333,26 @@
         <v>79</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>419</v>
+        <v>470</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>79</v>
@@ -21316,18 +21364,18 @@
         <v>79</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>345</v>
+        <v>134</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>420</v>
+        <v>187</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>79</v>
       </c>
@@ -21363,31 +21411,31 @@
         <v>79</v>
       </c>
       <c r="AB160" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC160" t="s" s="2">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="AD160" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE160" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>419</v>
+        <v>157</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>79</v>
@@ -21405,15 +21453,15 @@
         <v>79</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>423</v>
+        <v>472</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21424,7 +21472,7 @@
         <v>80</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>79</v>
@@ -21433,20 +21481,22 @@
         <v>79</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>415</v>
+        <v>218</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>424</v>
+        <v>219</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N161" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N161" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="O161" t="s" s="2">
-        <v>426</v>
+        <v>222</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>79</v>
@@ -21495,13 +21545,13 @@
         <v>79</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>79</v>
@@ -21525,15 +21575,15 @@
         <v>79</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>79</v>
+        <v>224</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>427</v>
+        <v>474</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21547,26 +21597,28 @@
         <v>89</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>366</v>
+        <v>149</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>428</v>
+        <v>227</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N162" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O162" t="s" s="2">
-        <v>422</v>
+        <v>230</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>79</v>
@@ -21576,7 +21628,7 @@
         <v>79</v>
       </c>
       <c r="S162" t="s" s="2">
-        <v>79</v>
+        <v>567</v>
       </c>
       <c r="T162" t="s" s="2">
         <v>79</v>
@@ -21615,7 +21667,7 @@
         <v>79</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>427</v>
+        <v>232</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -21630,7 +21682,7 @@
         <v>101</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>79</v>
+        <v>568</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>79</v>
@@ -21645,15 +21697,15 @@
         <v>79</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>556</v>
+        <v>569</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21676,17 +21728,17 @@
         <v>79</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>79</v>
@@ -21735,7 +21787,7 @@
         <v>79</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -21770,10 +21822,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21799,14 +21851,14 @@
         <v>345</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>79</v>
@@ -21855,7 +21907,7 @@
         <v>79</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -21890,10 +21942,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21907,7 +21959,7 @@
         <v>89</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>79</v>
@@ -21916,17 +21968,17 @@
         <v>79</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>79</v>
@@ -21975,7 +22027,7 @@
         <v>79</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -21990,10 +22042,10 @@
         <v>101</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>559</v>
+        <v>79</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>560</v>
+        <v>79</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>79</v>
@@ -22010,10 +22062,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>561</v>
+        <v>444</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22036,19 +22088,17 @@
         <v>79</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>562</v>
+        <v>445</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>565</v>
+        <v>439</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>79</v>
@@ -22073,13 +22123,13 @@
         <v>79</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>566</v>
+        <v>79</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>567</v>
+        <v>79</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>79</v>
@@ -22097,7 +22147,7 @@
         <v>79</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>561</v>
+        <v>444</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22132,10 +22182,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>568</v>
+        <v>447</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22146,7 +22196,7 @@
         <v>80</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>79</v>
@@ -22158,17 +22208,17 @@
         <v>79</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>387</v>
+        <v>448</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>569</v>
+        <v>449</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>570</v>
+        <v>450</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>571</v>
+        <v>451</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>79</v>
@@ -22217,13 +22267,13 @@
         <v>79</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>568</v>
+        <v>447</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>79</v>
@@ -22252,10 +22302,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>572</v>
+        <v>452</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22278,16 +22328,18 @@
         <v>79</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>149</v>
+        <v>345</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>150</v>
+        <v>453</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>151</v>
+        <v>454</v>
       </c>
       <c r="N168" s="2"/>
-      <c r="O168" s="2"/>
+      <c r="O168" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P168" t="s" s="2">
         <v>79</v>
       </c>
@@ -22335,7 +22387,7 @@
         <v>79</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>152</v>
+        <v>452</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22347,7 +22399,7 @@
         <v>79</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>79</v>
@@ -22365,29 +22417,29 @@
         <v>79</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>573</v>
+        <v>455</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H169" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I169" t="s" s="2">
         <v>79</v>
@@ -22396,18 +22448,18 @@
         <v>79</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>134</v>
+        <v>373</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>187</v>
+        <v>456</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O169" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N169" s="2"/>
+      <c r="O169" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="P169" t="s" s="2">
         <v>79</v>
       </c>
@@ -22455,25 +22507,25 @@
         <v>79</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>157</v>
+        <v>455</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>79</v>
+        <v>576</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>79</v>
+        <v>577</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>79</v>
@@ -22485,50 +22537,50 @@
         <v>79</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I170" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>396</v>
+        <v>579</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>397</v>
+        <v>580</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>189</v>
+        <v>581</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>282</v>
+        <v>582</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>79</v>
@@ -22553,13 +22605,13 @@
         <v>79</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>79</v>
+        <v>583</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>79</v>
+        <v>584</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>79</v>
@@ -22577,19 +22629,19 @@
         <v>79</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>398</v>
+        <v>578</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>79</v>
@@ -22607,15 +22659,15 @@
         <v>79</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22626,7 +22678,7 @@
         <v>80</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>79</v>
@@ -22638,17 +22690,17 @@
         <v>79</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>109</v>
+        <v>404</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>79</v>
@@ -22673,13 +22725,13 @@
         <v>79</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>196</v>
+        <v>79</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>579</v>
+        <v>79</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>580</v>
+        <v>79</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>79</v>
@@ -22697,13 +22749,13 @@
         <v>79</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>79</v>
@@ -22732,10 +22784,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22761,15 +22813,13 @@
         <v>149</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>582</v>
+        <v>150</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>583</v>
+        <v>151</v>
       </c>
       <c r="N172" s="2"/>
-      <c r="O172" t="s" s="2">
-        <v>584</v>
-      </c>
+      <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>79</v>
       </c>
@@ -22817,7 +22867,7 @@
         <v>79</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>581</v>
+        <v>152</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -22829,29 +22879,511 @@
         <v>79</v>
       </c>
       <c r="AJ172" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK172" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL172" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM172" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN172" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO172" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP172" t="s" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="173" hidden="true">
+      <c r="A173" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="E173" s="2"/>
+      <c r="F173" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K173" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L173" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M173" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O173" s="2"/>
+      <c r="P173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q173" s="2"/>
+      <c r="R173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF173" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG173" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP173" t="s" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="174" hidden="true">
+      <c r="A174" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J174" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K174" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="P174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q174" s="2"/>
+      <c r="R174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ174" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP174" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="175" hidden="true">
+      <c r="A175" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C175" s="2"/>
+      <c r="D175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E175" s="2"/>
+      <c r="F175" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G175" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K175" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L175" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M175" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N175" s="2"/>
+      <c r="O175" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="P175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q175" s="2"/>
+      <c r="R175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X175" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="Z175" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AA175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF175" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AG175" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH175" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ175" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK172" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL172" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM172" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN172" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO172" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AP172" t="s" s="2">
+      <c r="AK175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP175" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="176" hidden="true">
+      <c r="A176" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C176" s="2"/>
+      <c r="D176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E176" s="2"/>
+      <c r="F176" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G176" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K176" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L176" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M176" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N176" s="2"/>
+      <c r="O176" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="P176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q176" s="2"/>
+      <c r="R176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF176" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG176" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH176" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ176" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO176" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AP176" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP172">
+  <autoFilter ref="A1:AP176">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -22861,7 +23393,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI171">
+  <conditionalFormatting sqref="A2:AI175">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
+++ b/docs/StructureDefinition-DebtPortalPaymentReconciliation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
